--- a/data/file_generation/reference/data_107/B店_揽收明细_res.xlsx
+++ b/data/file_generation/reference/data_107/B店_揽收明细_res.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chenyanbing/files/26/0206/data_107/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chenyanbing/files/26/0205/ai办公标注/output/data_107/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2648FB6-4DB6-BC45-9D89-67C4FC21097A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52000597-62B7-064B-9CAF-357DB644AE2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1080" yWindow="500" windowWidth="34760" windowHeight="21900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -62,9 +62,6 @@
     <t>客户B</t>
   </si>
   <si>
-    <t>2025-10-23 18:54:01</t>
-  </si>
-  <si>
     <t>贵州省</t>
   </si>
   <si>
@@ -72,6 +69,9 @@
   </si>
   <si>
     <t>运单总数量: 1</t>
+  </si>
+  <si>
+    <t>2025年10月</t>
   </si>
 </sst>
 </file>
@@ -472,10 +472,10 @@
         <v>8</v>
       </c>
       <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
         <v>9</v>
-      </c>
-      <c r="D2" t="s">
-        <v>10</v>
       </c>
       <c r="E2">
         <v>0.2</v>
@@ -484,10 +484,10 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="G2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>12</v>
       </c>
       <c r="I2">
         <f>ROUND(2.2-1*1.8,2)</f>
@@ -664,13 +664,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{839CF294-1D93-49DB-BFD2-2152FAD946F9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3732D2D4-C285-4CA5-A58F-2EDDBC1845F3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{206252D8-128A-4971-87D8-D07DBB137C01}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D95534D3-1C9F-436E-A310-48FB30CF8C95}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8ABE3CD-1CD5-45CD-B128-4AC7926977FF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15F31912-9458-49A0-BBDD-DB97E6F48171}"/>
 </file>